--- a/data/sample/synthetic_cost.xlsx
+++ b/data/sample/synthetic_cost.xlsx
@@ -465,7 +465,7 @@
         <v>46082</v>
       </c>
       <c r="D2" t="n">
-        <v>611967597.1</v>
+        <v>249825832.11</v>
       </c>
     </row>
     <row r="3">
@@ -479,7 +479,7 @@
         <v>46113</v>
       </c>
       <c r="D3" t="n">
-        <v>500180885.3</v>
+        <v>363396664.31</v>
       </c>
     </row>
     <row r="4">
@@ -493,7 +493,7 @@
         <v>46143</v>
       </c>
       <c r="D4" t="n">
-        <v>598040629.4400001</v>
+        <v>385188237.96</v>
       </c>
     </row>
     <row r="5">
@@ -507,7 +507,7 @@
         <v>46174</v>
       </c>
       <c r="D5" t="n">
-        <v>242161213.06</v>
+        <v>753873421.53</v>
       </c>
     </row>
     <row r="6">
@@ -521,7 +521,7 @@
         <v>46204</v>
       </c>
       <c r="D6" t="n">
-        <v>872076144.2</v>
+        <v>612852712.4400001</v>
       </c>
     </row>
     <row r="7">
@@ -535,7 +535,7 @@
         <v>46235</v>
       </c>
       <c r="D7" t="n">
-        <v>269463502.34</v>
+        <v>762733976.2</v>
       </c>
     </row>
     <row r="8">
@@ -549,7 +549,7 @@
         <v>46082</v>
       </c>
       <c r="D8" t="n">
-        <v>733915973.05</v>
+        <v>338473449.63</v>
       </c>
     </row>
     <row r="9">
@@ -563,7 +563,7 @@
         <v>46113</v>
       </c>
       <c r="D9" t="n">
-        <v>637860521.28</v>
+        <v>280343411.72</v>
       </c>
     </row>
     <row r="10">
@@ -577,7 +577,7 @@
         <v>46143</v>
       </c>
       <c r="D10" t="n">
-        <v>385252287.7</v>
+        <v>357366615.19</v>
       </c>
     </row>
     <row r="11">
@@ -591,7 +591,7 @@
         <v>46174</v>
       </c>
       <c r="D11" t="n">
-        <v>256831225.83</v>
+        <v>304292580.75</v>
       </c>
     </row>
     <row r="12">
@@ -605,7 +605,7 @@
         <v>46204</v>
       </c>
       <c r="D12" t="n">
-        <v>367905624.37</v>
+        <v>385942730.15</v>
       </c>
     </row>
     <row r="13">
@@ -619,7 +619,7 @@
         <v>46235</v>
       </c>
       <c r="D13" t="n">
-        <v>586394571.9</v>
+        <v>299565399.81</v>
       </c>
     </row>
     <row r="14">
@@ -633,7 +633,7 @@
         <v>46082</v>
       </c>
       <c r="D14" t="n">
-        <v>309572830.81</v>
+        <v>241746627.66</v>
       </c>
     </row>
     <row r="15">
@@ -647,7 +647,7 @@
         <v>46113</v>
       </c>
       <c r="D15" t="n">
-        <v>485962300.86</v>
+        <v>754839996.36</v>
       </c>
     </row>
     <row r="16">
@@ -661,7 +661,7 @@
         <v>46143</v>
       </c>
       <c r="D16" t="n">
-        <v>682559795.05</v>
+        <v>616530826.12</v>
       </c>
     </row>
     <row r="17">
@@ -675,7 +675,7 @@
         <v>46174</v>
       </c>
       <c r="D17" t="n">
-        <v>528938735.31</v>
+        <v>776968210.92</v>
       </c>
     </row>
     <row r="18">
@@ -689,7 +689,7 @@
         <v>46204</v>
       </c>
       <c r="D18" t="n">
-        <v>222847898.77</v>
+        <v>844834770.28</v>
       </c>
     </row>
     <row r="19">
@@ -703,7 +703,7 @@
         <v>46235</v>
       </c>
       <c r="D19" t="n">
-        <v>401673422.72</v>
+        <v>507407414.07</v>
       </c>
     </row>
     <row r="20">
@@ -717,7 +717,7 @@
         <v>46082</v>
       </c>
       <c r="D20" t="n">
-        <v>397902861.18</v>
+        <v>528088579.19</v>
       </c>
     </row>
     <row r="21">
@@ -731,7 +731,7 @@
         <v>46113</v>
       </c>
       <c r="D21" t="n">
-        <v>801724711.9400001</v>
+        <v>412863833.38</v>
       </c>
     </row>
     <row r="22">
@@ -745,7 +745,7 @@
         <v>46143</v>
       </c>
       <c r="D22" t="n">
-        <v>249825832.11</v>
+        <v>481755963.41</v>
       </c>
     </row>
     <row r="23">
@@ -759,7 +759,7 @@
         <v>46174</v>
       </c>
       <c r="D23" t="n">
-        <v>363396664.31</v>
+        <v>390572335.2</v>
       </c>
     </row>
     <row r="24">
@@ -773,7 +773,7 @@
         <v>46204</v>
       </c>
       <c r="D24" t="n">
-        <v>385188237.96</v>
+        <v>577987093.8200001</v>
       </c>
     </row>
     <row r="25">
@@ -787,7 +787,7 @@
         <v>46235</v>
       </c>
       <c r="D25" t="n">
-        <v>753873421.53</v>
+        <v>506431204.5</v>
       </c>
     </row>
     <row r="26">
@@ -801,7 +801,7 @@
         <v>46082</v>
       </c>
       <c r="D26" t="n">
-        <v>612852712.4400001</v>
+        <v>618625663.4299999</v>
       </c>
     </row>
     <row r="27">
@@ -815,7 +815,7 @@
         <v>46113</v>
       </c>
       <c r="D27" t="n">
-        <v>762733976.2</v>
+        <v>822596022.5</v>
       </c>
     </row>
     <row r="28">
@@ -829,7 +829,7 @@
         <v>46143</v>
       </c>
       <c r="D28" t="n">
-        <v>338473449.63</v>
+        <v>714173746.3</v>
       </c>
     </row>
     <row r="29">
@@ -843,7 +843,7 @@
         <v>46174</v>
       </c>
       <c r="D29" t="n">
-        <v>280343411.72</v>
+        <v>622599548.66</v>
       </c>
     </row>
     <row r="30">
@@ -857,7 +857,7 @@
         <v>46204</v>
       </c>
       <c r="D30" t="n">
-        <v>357366615.19</v>
+        <v>218105424.67</v>
       </c>
     </row>
     <row r="31">
@@ -871,7 +871,7 @@
         <v>46235</v>
       </c>
       <c r="D31" t="n">
-        <v>304292580.75</v>
+        <v>360247091.01</v>
       </c>
     </row>
   </sheetData>
